--- a/education_forms/012_child_education_sponsorship_donation_form--education_forms.xlsx
+++ b/education_forms/012_child_education_sponsorship_donation_form--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -862,8 +862,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="35" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -891,12 +891,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'one-time_gift',_'value':_'onetime'}</t>
+          <t>one-time_gift</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'One-time Gift', 'value': 'onetime'}</t>
+          <t>One-time Gift</t>
         </is>
       </c>
     </row>
@@ -908,12 +908,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'monthly_recurring',_'value':_'monthly'}</t>
+          <t>monthly_recurring</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Monthly Recurring', 'value': 'monthly'}</t>
+          <t>Monthly Recurring</t>
         </is>
       </c>
     </row>
@@ -925,12 +925,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'annual_sponsorship',_'value':_'annual'}</t>
+          <t>annual_sponsorship</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Annual Sponsorship', 'value': 'annual'}</t>
+          <t>Annual Sponsorship</t>
         </is>
       </c>
     </row>
@@ -942,12 +942,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'$25_-_monthly_support',_'value':_'25'}</t>
+          <t>$25_-_monthly_support</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': '$25 - Monthly Support', 'value': '25'}</t>
+          <t>$25 - Monthly Support</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'$50_-_supply_kit',_'value':_'50'}</t>
+          <t>$50_-_supply_kit</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': '$50 - Supply Kit', 'value': '50'}</t>
+          <t>$50 - Supply Kit</t>
         </is>
       </c>
     </row>
@@ -976,12 +976,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'$100_-_tuition_assistance',_'value':_'100'}</t>
+          <t>$100_-_tuition_assistance</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': '$100 - Tuition Assistance', 'value': '100'}</t>
+          <t>$100 - Tuition Assistance</t>
         </is>
       </c>
     </row>
@@ -993,12 +993,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'$500_-_major_initiative',_'value':_'500'}</t>
+          <t>$500_-_major_initiative</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': '$500 - Major Initiative', 'value': '500'}</t>
+          <t>$500 - Major Initiative</t>
         </is>
       </c>
     </row>
@@ -1010,12 +1010,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'custom_amount',_'value':_'custom'}</t>
+          <t>custom_amount</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Custom Amount', 'value': 'custom'}</t>
+          <t>Custom Amount</t>
         </is>
       </c>
     </row>
@@ -1027,12 +1027,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'student_scholarships',_'value':_'scholarships'}</t>
+          <t>student_scholarships</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Student Scholarships', 'value': 'scholarships'}</t>
+          <t>Student Scholarships</t>
         </is>
       </c>
     </row>
@@ -1044,12 +1044,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'school_supplies_and_tech',_'value':_'supplies'}</t>
+          <t>school_supplies_and_tech</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'School Supplies and Tech', 'value': 'supplies'}</t>
+          <t>School Supplies and Tech</t>
         </is>
       </c>
     </row>
@@ -1061,12 +1061,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'teacher_training',_'value':_'training'}</t>
+          <t>teacher_training</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Teacher Training', 'value': 'training'}</t>
+          <t>Teacher Training</t>
         </is>
       </c>
     </row>
@@ -1078,12 +1078,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'facility_improvements',_'value':_'facilities'}</t>
+          <t>facility_improvements</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Facility Improvements', 'value': 'facilities'}</t>
+          <t>Facility Improvements</t>
         </is>
       </c>
     </row>
@@ -1095,12 +1095,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'credit_or_debit_card',_'value':_'card'}</t>
+          <t>credit_or_debit_card</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Credit or Debit Card', 'value': 'card'}</t>
+          <t>Credit or Debit Card</t>
         </is>
       </c>
     </row>
@@ -1112,12 +1112,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'paypal',_'value':_'paypal'}</t>
+          <t>paypal</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'PayPal', 'value': 'paypal'}</t>
+          <t>PayPal</t>
         </is>
       </c>
     </row>
@@ -1129,12 +1129,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'bank_transfer_(ach)',_'value':_'ach'}</t>
+          <t>bank_transfer_(ach)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Bank Transfer (ACH)', 'value': 'ach'}</t>
+          <t>Bank Transfer (ACH)</t>
         </is>
       </c>
     </row>
@@ -1146,12 +1146,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'yes_-_keep_my_donation_anonymous',_'value':_true}</t>
+          <t>yes_-_keep_my_donation_anonymous</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Yes - Keep my donation anonymous', 'value': True}</t>
+          <t>Yes - Keep my donation anonymous</t>
         </is>
       </c>
     </row>
@@ -1163,12 +1163,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'no_-_publicly_acknowledge_my_gift',_'value':_false}</t>
+          <t>no_-_publicly_acknowledge_my_gift</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'No - Publicly acknowledge my gift', 'value': False}</t>
+          <t>No - Publicly acknowledge my gift</t>
         </is>
       </c>
     </row>
